--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DF01BD-FDE2-48E9-A776-CF8376CA329D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434716EE-A5EB-4C91-87CE-E78BCA69020D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,6 +200,22 @@
   </si>
   <si>
     <t>화살 사용하는 타워</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SlowEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체에 공격력 50 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체에 슬로우 효과 50%를 부여</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -526,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -702,135 +718,123 @@
         <v>40</v>
       </c>
     </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7">
+        <v>300</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
+    </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F8" t="s">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8">
+        <v>300</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
+      <c r="K8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>3</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
         <v>3</v>
       </c>
-      <c r="C9">
+      <c r="C11">
         <v>100</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F11" t="s">
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14">
         <v>200</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>34</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E14" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F14" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E15" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
         <v>28</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F17" t="s">
         <v>35</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G17" t="s">
         <v>9</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H17" t="s">
         <v>31</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I17" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16">
-        <v>150</v>
-      </c>
-      <c r="D16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-      <c r="F16">
-        <v>0.7</v>
-      </c>
-      <c r="G16">
-        <v>50</v>
-      </c>
-      <c r="H16">
-        <v>3</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17">
-        <v>200</v>
-      </c>
-      <c r="D17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17">
-        <v>10</v>
-      </c>
-      <c r="F17">
-        <v>1.2</v>
-      </c>
-      <c r="G17">
-        <v>35</v>
-      </c>
-      <c r="H17">
-        <v>5</v>
-      </c>
-      <c r="I17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K17" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -838,30 +842,94 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C18">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="D18" t="s">
         <v>34</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="G18">
         <v>50</v>
       </c>
       <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>200</v>
+      </c>
+      <c r="D19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19">
         <v>10</v>
       </c>
-      <c r="I18" t="s">
+      <c r="F19">
+        <v>1.2</v>
+      </c>
+      <c r="G19">
+        <v>35</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20">
+        <v>600</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20">
+        <v>15</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>50</v>
+      </c>
+      <c r="H20">
+        <v>10</v>
+      </c>
+      <c r="I20" t="s">
         <v>17</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K20" t="s">
         <v>42</v>
       </c>
     </row>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434716EE-A5EB-4C91-87CE-E78BCA69020D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E06641A-C595-4283-B63E-9DA7D3441499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -216,6 +216,29 @@
   </si>
   <si>
     <t>투사체에 슬로우 효과 50%를 부여</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마을, 방어구역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어구역</t>
+  </si>
+  <si>
+    <t>나무, 쇠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무와 쇠로 망치를 만드는 공장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HammerFactory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>망치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -542,11 +565,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="15.375" customWidth="1"/>
+    <col min="3" max="3" width="13.375" customWidth="1"/>
     <col min="4" max="4" width="34.125" customWidth="1"/>
     <col min="5" max="5" width="19.75" customWidth="1"/>
     <col min="6" max="6" width="27.75" customWidth="1"/>
@@ -587,7 +611,7 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -596,56 +620,21 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F3" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H4" t="s">
         <v>31</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I4" t="s">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J4" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -653,7 +642,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>150</v>
@@ -668,19 +657,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -688,13 +677,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -703,19 +692,19 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -723,13 +712,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -737,11 +726,20 @@
       <c r="F7">
         <v>1</v>
       </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>25</v>
+      </c>
       <c r="J7">
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -749,156 +747,153 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>400</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
+      <c r="K8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>300</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
         <v>45</v>
       </c>
-      <c r="C8">
+      <c r="C10">
         <v>300</v>
       </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F10" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>3</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
         <v>3</v>
       </c>
-      <c r="C11">
+      <c r="C13">
         <v>100</v>
       </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F13" t="s">
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16">
         <v>200</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D16" t="s">
         <v>34</v>
       </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E17" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
         <v>28</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F19" t="s">
         <v>35</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G19" t="s">
         <v>9</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H19" t="s">
         <v>31</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I19" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18">
-        <v>150</v>
-      </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18">
-        <v>6</v>
-      </c>
-      <c r="F18">
-        <v>0.7</v>
-      </c>
-      <c r="G18">
-        <v>50</v>
-      </c>
-      <c r="H18">
-        <v>3</v>
-      </c>
-      <c r="I18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19">
-        <v>200</v>
-      </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19">
-        <v>10</v>
-      </c>
-      <c r="F19">
-        <v>1.2</v>
-      </c>
-      <c r="G19">
-        <v>35</v>
-      </c>
-      <c r="H19">
-        <v>5</v>
-      </c>
-      <c r="I19" t="s">
-        <v>16</v>
-      </c>
-      <c r="K19" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -906,30 +901,94 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C20">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="D20" t="s">
         <v>34</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="G20">
         <v>50</v>
       </c>
       <c r="H20">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I20" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>200</v>
+      </c>
+      <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>1.2</v>
+      </c>
+      <c r="G21">
+        <v>35</v>
+      </c>
+      <c r="H21">
+        <v>5</v>
+      </c>
+      <c r="I21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22">
+        <v>600</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22">
+        <v>15</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>50</v>
+      </c>
+      <c r="H22">
+        <v>10</v>
+      </c>
+      <c r="I22" t="s">
         <v>17</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K22" t="s">
         <v>42</v>
       </c>
     </row>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E06641A-C595-4283-B63E-9DA7D3441499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F02FD3D-F6A0-4B4D-A3C9-0321DBB05E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="53">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -56,10 +56,6 @@
   </si>
   <si>
     <t>Archer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -565,22 +561,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="15.375" customWidth="1"/>
-    <col min="3" max="3" width="13.375" customWidth="1"/>
-    <col min="4" max="4" width="34.125" customWidth="1"/>
-    <col min="5" max="5" width="19.75" customWidth="1"/>
-    <col min="6" max="6" width="27.75" customWidth="1"/>
-    <col min="7" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="15.375" customWidth="1"/>
-    <col min="10" max="10" width="29.875" customWidth="1"/>
-    <col min="11" max="11" width="90.25" customWidth="1"/>
+    <col min="3" max="3" width="34.125" customWidth="1"/>
+    <col min="4" max="4" width="19.75" customWidth="1"/>
+    <col min="5" max="5" width="27.75" customWidth="1"/>
+    <col min="6" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="15.375" customWidth="1"/>
+    <col min="9" max="9" width="29.875" customWidth="1"/>
+    <col min="10" max="10" width="90.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -588,408 +583,369 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>100</v>
+      <c r="C2" t="s">
+        <v>47</v>
       </c>
       <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
         <v>48</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
         <v>23</v>
       </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5">
-        <v>150</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>150</v>
-      </c>
-      <c r="D7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8">
-        <v>400</v>
-      </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-      <c r="K8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9">
-        <v>300</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
-      <c r="K9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10">
-        <v>300</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>5</v>
-      </c>
-      <c r="K10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
       </c>
-      <c r="C13">
-        <v>100</v>
+      <c r="C13" t="s">
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
-      <c r="C16">
-        <v>200</v>
+      <c r="C16" t="s">
+        <v>33</v>
       </c>
       <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
         <v>34</v>
       </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E19" t="s">
-        <v>28</v>
-      </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20">
-        <v>150</v>
-      </c>
-      <c r="D20" t="s">
-        <v>34</v>
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20">
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="F20">
-        <v>0.7</v>
+        <v>50</v>
       </c>
       <c r="G20">
-        <v>50</v>
-      </c>
-      <c r="H20">
         <v>3</v>
       </c>
-      <c r="I20" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
       </c>
-      <c r="C21">
-        <v>200</v>
-      </c>
-      <c r="D21" t="s">
-        <v>34</v>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="F21">
-        <v>1.2</v>
+        <v>35</v>
       </c>
       <c r="G21">
-        <v>35</v>
-      </c>
-      <c r="H21">
-        <v>5</v>
-      </c>
-      <c r="I21" t="s">
-        <v>16</v>
-      </c>
-      <c r="K21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22">
-        <v>600</v>
-      </c>
-      <c r="D22" t="s">
-        <v>34</v>
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22">
+        <v>15</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G22">
-        <v>50</v>
-      </c>
-      <c r="H22">
         <v>10</v>
       </c>
-      <c r="I22" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" t="s">
-        <v>42</v>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F02FD3D-F6A0-4B4D-A3C9-0321DBB05E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4C5DBC-EEDA-4665-8E37-673354BD4DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="66">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -235,6 +235,58 @@
   </si>
   <si>
     <t>망치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>망치 공장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 공장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살 공장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총알 공장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화력 제련소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉기 제련소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공장 가속소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타워 강화소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새총</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>궁수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -561,21 +613,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="15.375" customWidth="1"/>
-    <col min="3" max="3" width="34.125" customWidth="1"/>
-    <col min="4" max="4" width="19.75" customWidth="1"/>
-    <col min="5" max="5" width="27.75" customWidth="1"/>
-    <col min="6" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="15.375" customWidth="1"/>
-    <col min="9" max="9" width="29.875" customWidth="1"/>
-    <col min="10" max="10" width="90.25" customWidth="1"/>
+    <col min="2" max="3" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="34.125" customWidth="1"/>
+    <col min="5" max="5" width="19.75" customWidth="1"/>
+    <col min="6" max="6" width="27.75" customWidth="1"/>
+    <col min="7" max="8" width="17.5" customWidth="1"/>
+    <col min="9" max="9" width="15.375" customWidth="1"/>
+    <col min="10" max="10" width="29.875" customWidth="1"/>
+    <col min="11" max="11" width="90.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -583,16 +635,19 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -600,33 +655,36 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
         <v>47</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E4" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>21</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -634,31 +692,34 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>9</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
         <v>52</v>
       </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
         <v>49</v>
       </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -666,31 +727,34 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
         <v>48</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>9</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
         <v>25</v>
       </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6" t="s">
         <v>14</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -698,31 +762,34 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
         <v>48</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>9</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
         <v>15</v>
       </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7" t="s">
         <v>24</v>
       </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -730,31 +797,34 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s">
         <v>48</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>9</v>
       </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
         <v>16</v>
       </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8" t="s">
         <v>26</v>
       </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="J8">
+        <v>5</v>
+      </c>
+      <c r="K8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -762,22 +832,25 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" t="s">
         <v>48</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>9</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>5</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -785,27 +858,30 @@
         <v>44</v>
       </c>
       <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>9</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>5</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E12" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -813,21 +889,24 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
         <v>48</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E15" t="s">
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -835,33 +914,36 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
         <v>33</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
         <v>27</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>34</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>8</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>30</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -869,28 +951,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
         <v>33</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>6</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.7</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>50</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>3</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>25</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -898,28 +983,31 @@
         <v>7</v>
       </c>
       <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" t="s">
         <v>33</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>10</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>1.2</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>35</v>
       </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="H21">
+        <v>5</v>
+      </c>
+      <c r="I21" t="s">
         <v>15</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -927,24 +1015,27 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" t="s">
         <v>33</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>15</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>2</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>50</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>10</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>16</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>41</v>
       </c>
     </row>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4C5DBC-EEDA-4665-8E37-673354BD4DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBFA962-64A0-448F-8BC5-DF446ABCD800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -139,10 +139,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>초당 재료 생산(공장만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>필요재료 최대 수용량</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -287,6 +283,21 @@
   </si>
   <si>
     <t>총</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forge</t>
+  </si>
+  <si>
+    <t>초당 재료 생산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화된 투사체</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -613,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -635,16 +646,16 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
         <v>11</v>
       </c>
       <c r="K1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -655,33 +666,33 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F4" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
         <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -689,13 +700,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -704,19 +715,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5" t="s">
         <v>49</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -727,10 +738,10 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -751,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -762,10 +773,10 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -786,7 +797,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -797,10 +808,10 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -821,47 +832,21 @@
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
-      <c r="K9" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -869,6 +854,12 @@
       <c r="F10">
         <v>1</v>
       </c>
+      <c r="G10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" t="s">
+        <v>65</v>
+      </c>
       <c r="J10">
         <v>5</v>
       </c>
@@ -876,103 +867,103 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F12" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11">
+        <v>5</v>
+      </c>
+      <c r="K11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>3</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>3</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
         <v>61</v>
       </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="F17" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" t="s">
         <v>33</v>
       </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="G20" t="s">
         <v>8</v>
       </c>
-      <c r="H19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="H20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20">
-        <v>6</v>
-      </c>
-      <c r="F20">
-        <v>0.7</v>
-      </c>
-      <c r="G20">
-        <v>50</v>
-      </c>
-      <c r="H20">
-        <v>3</v>
-      </c>
-      <c r="I20" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -980,31 +971,31 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -1012,31 +1003,63 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>1.2</v>
+      </c>
+      <c r="G22">
+        <v>35</v>
+      </c>
+      <c r="H22">
+        <v>5</v>
+      </c>
+      <c r="I22" t="s">
         <v>15</v>
-      </c>
-      <c r="F22">
-        <v>2</v>
-      </c>
-      <c r="G22">
-        <v>50</v>
-      </c>
-      <c r="H22">
-        <v>10</v>
-      </c>
-      <c r="I22" t="s">
-        <v>16</v>
       </c>
       <c r="K22" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23">
+        <v>15</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>50</v>
+      </c>
+      <c r="H23">
+        <v>10</v>
+      </c>
+      <c r="I23" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/0_Adventure/Deploy/타워 정보.xlsx
+++ b/Assets/0_Adventure/Deploy/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBFA962-64A0-448F-8BC5-DF446ABCD800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E09F688-D15B-4483-931D-B981F443C508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,18 +63,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1X1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>타워 공격력 증가량(타워 버프만)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>효과 범위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Slingshot</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -298,6 +290,18 @@
   </si>
   <si>
     <t>강화된 투사체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 채굴장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쇠 채굴장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -624,21 +628,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="3" width="15.375" customWidth="1"/>
     <col min="4" max="4" width="34.125" customWidth="1"/>
-    <col min="5" max="5" width="19.75" customWidth="1"/>
-    <col min="6" max="6" width="27.75" customWidth="1"/>
-    <col min="7" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="15.375" customWidth="1"/>
-    <col min="10" max="10" width="29.875" customWidth="1"/>
-    <col min="11" max="11" width="90.25" customWidth="1"/>
+    <col min="5" max="5" width="30.25" customWidth="1"/>
+    <col min="6" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="15.375" customWidth="1"/>
+    <col min="9" max="9" width="29.875" customWidth="1"/>
+    <col min="10" max="10" width="90.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -646,19 +649,16 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="J1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -666,400 +666,421 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
       <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>67</v>
       </c>
-      <c r="G4" t="s">
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="G5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
       <c r="I7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
         <v>57</v>
       </c>
-      <c r="D8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14">
+        <v>5</v>
+      </c>
+      <c r="J14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
         <v>9</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-      <c r="K8" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="F24">
+        <v>0.7</v>
+      </c>
+      <c r="G24">
+        <v>50</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>1.2</v>
+      </c>
+      <c r="G25">
+        <v>35</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26">
+        <v>15</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>50</v>
+      </c>
+      <c r="H26">
+        <v>10</v>
+      </c>
+      <c r="I26" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I10" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10">
-        <v>5</v>
-      </c>
-      <c r="K10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11">
-        <v>5</v>
-      </c>
-      <c r="K11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" t="s">
-        <v>29</v>
-      </c>
-      <c r="I20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21">
-        <v>6</v>
-      </c>
-      <c r="F21">
-        <v>0.7</v>
-      </c>
-      <c r="G21">
-        <v>50</v>
-      </c>
-      <c r="H21">
-        <v>3</v>
-      </c>
-      <c r="I21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22">
-        <v>10</v>
-      </c>
-      <c r="F22">
-        <v>1.2</v>
-      </c>
-      <c r="G22">
-        <v>35</v>
-      </c>
-      <c r="H22">
-        <v>5</v>
-      </c>
-      <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23">
-        <v>15</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="G23">
-        <v>50</v>
-      </c>
-      <c r="H23">
-        <v>10</v>
-      </c>
-      <c r="I23" t="s">
-        <v>16</v>
-      </c>
-      <c r="K23" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
